--- a/etf_holdings/2026-09-01_00980A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-01_00980A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-01 03:08:38</t>
+          <t>2026-09-01 03:15:22</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-01 03:08:38</t>
+          <t>2026-09-01 03:15:22</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-01 03:08:38</t>
+          <t>2026-09-01 03:15:22</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-01 03:08:38</t>
+          <t>2026-09-01 03:15:22</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-01 03:08:38</t>
+          <t>2026-09-01 03:15:22</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-01 03:08:38</t>
+          <t>2026-09-01 03:15:22</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-01 03:08:38</t>
+          <t>2026-09-01 03:15:22</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-01 03:08:38</t>
+          <t>2026-09-01 03:15:22</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-01 03:08:38</t>
+          <t>2026-09-01 03:15:22</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-01 03:08:38</t>
+          <t>2026-09-01 03:15:22</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-01 03:08:38</t>
+          <t>2026-09-01 03:15:22</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-01 03:08:38</t>
+          <t>2026-09-01 03:15:22</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-01 03:08:38</t>
+          <t>2026-09-01 03:15:22</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-01 03:08:38</t>
+          <t>2026-09-01 03:15:22</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-01 03:08:38</t>
+          <t>2026-09-01 03:15:22</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-01 03:08:40</t>
+          <t>2026-09-01 03:15:23</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-01 03:08:40</t>
+          <t>2026-09-01 03:15:23</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-01 03:08:40</t>
+          <t>2026-09-01 03:15:23</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-01 03:08:40</t>
+          <t>2026-09-01 03:15:23</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-01 03:08:40</t>
+          <t>2026-09-01 03:15:23</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-01 03:08:40</t>
+          <t>2026-09-01 03:15:23</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-01 03:08:40</t>
+          <t>2026-09-01 03:15:23</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-01 03:08:40</t>
+          <t>2026-09-01 03:15:23</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-01 03:08:40</t>
+          <t>2026-09-01 03:15:23</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-01 03:08:40</t>
+          <t>2026-09-01 03:15:23</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-01 03:08:40</t>
+          <t>2026-09-01 03:15:23</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-01 03:08:40</t>
+          <t>2026-09-01 03:15:23</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-01 03:08:40</t>
+          <t>2026-09-01 03:15:23</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-01 03:08:40</t>
+          <t>2026-09-01 03:15:23</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-01 03:08:40</t>
+          <t>2026-09-01 03:15:23</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-01 03:08:41</t>
+          <t>2026-09-01 03:15:24</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-01 03:08:41</t>
+          <t>2026-09-01 03:15:24</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-01 03:08:41</t>
+          <t>2026-09-01 03:15:24</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-01 03:08:41</t>
+          <t>2026-09-01 03:15:24</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-01 03:08:41</t>
+          <t>2026-09-01 03:15:24</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-01 03:08:41</t>
+          <t>2026-09-01 03:15:24</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-01 03:08:41</t>
+          <t>2026-09-01 03:15:24</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-01 03:08:41</t>
+          <t>2026-09-01 03:15:24</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-01 03:08:41</t>
+          <t>2026-09-01 03:15:24</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-01 03:08:41</t>
+          <t>2026-09-01 03:15:24</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-01 03:08:41</t>
+          <t>2026-09-01 03:15:24</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-01 03:08:41</t>
+          <t>2026-09-01 03:15:24</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-01 03:08:41</t>
+          <t>2026-09-01 03:15:24</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-01 03:08:41</t>
+          <t>2026-09-01 03:15:24</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-01 03:08:41</t>
+          <t>2026-09-01 03:15:24</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-09-01 03:08:42</t>
+          <t>2026-09-01 03:15:26</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-09-01 03:08:42</t>
+          <t>2026-09-01 03:15:26</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-01 03:08:42</t>
+          <t>2026-09-01 03:15:26</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-09-01 03:08:42</t>
+          <t>2026-09-01 03:15:26</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-09-01 03:08:42</t>
+          <t>2026-09-01 03:15:26</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">

--- a/etf_holdings/2026-09-01_00980A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-01_00980A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:22</t>
+          <t>2026-09-01 03:32:06</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:22</t>
+          <t>2026-09-01 03:32:06</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:22</t>
+          <t>2026-09-01 03:32:06</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:22</t>
+          <t>2026-09-01 03:32:06</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:22</t>
+          <t>2026-09-01 03:32:06</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:22</t>
+          <t>2026-09-01 03:32:06</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:22</t>
+          <t>2026-09-01 03:32:06</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:22</t>
+          <t>2026-09-01 03:32:06</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:22</t>
+          <t>2026-09-01 03:32:06</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:22</t>
+          <t>2026-09-01 03:32:06</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:22</t>
+          <t>2026-09-01 03:32:06</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:22</t>
+          <t>2026-09-01 03:32:06</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:22</t>
+          <t>2026-09-01 03:32:06</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:22</t>
+          <t>2026-09-01 03:32:06</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:22</t>
+          <t>2026-09-01 03:32:06</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:23</t>
+          <t>2026-09-01 03:32:08</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:23</t>
+          <t>2026-09-01 03:32:08</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:23</t>
+          <t>2026-09-01 03:32:08</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:23</t>
+          <t>2026-09-01 03:32:08</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:23</t>
+          <t>2026-09-01 03:32:08</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:23</t>
+          <t>2026-09-01 03:32:08</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:23</t>
+          <t>2026-09-01 03:32:08</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:23</t>
+          <t>2026-09-01 03:32:08</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:23</t>
+          <t>2026-09-01 03:32:08</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:23</t>
+          <t>2026-09-01 03:32:08</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:23</t>
+          <t>2026-09-01 03:32:08</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:23</t>
+          <t>2026-09-01 03:32:08</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:23</t>
+          <t>2026-09-01 03:32:08</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:23</t>
+          <t>2026-09-01 03:32:08</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:23</t>
+          <t>2026-09-01 03:32:08</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:24</t>
+          <t>2026-09-01 03:32:09</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:24</t>
+          <t>2026-09-01 03:32:09</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:24</t>
+          <t>2026-09-01 03:32:09</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:24</t>
+          <t>2026-09-01 03:32:09</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:24</t>
+          <t>2026-09-01 03:32:09</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:24</t>
+          <t>2026-09-01 03:32:09</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:24</t>
+          <t>2026-09-01 03:32:09</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:24</t>
+          <t>2026-09-01 03:32:09</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:24</t>
+          <t>2026-09-01 03:32:09</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:24</t>
+          <t>2026-09-01 03:32:09</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:24</t>
+          <t>2026-09-01 03:32:09</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:24</t>
+          <t>2026-09-01 03:32:09</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:24</t>
+          <t>2026-09-01 03:32:09</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:24</t>
+          <t>2026-09-01 03:32:09</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:24</t>
+          <t>2026-09-01 03:32:09</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:26</t>
+          <t>2026-09-01 03:32:10</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:26</t>
+          <t>2026-09-01 03:32:10</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:26</t>
+          <t>2026-09-01 03:32:10</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:26</t>
+          <t>2026-09-01 03:32:10</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:26</t>
+          <t>2026-09-01 03:32:10</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">

--- a/etf_holdings/2026-09-01_00980A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-01_00980A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-01 03:32:06</t>
+          <t>2026-09-01 15:28:38</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -509,25 +509,25 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>-0.62%2405</t>
+          <t>+1.46%2440</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-0.62%</t>
+          <t>+1.46%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>2405</v>
+        <v>2440</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>8.92%753,000</t>
+          <t>8.96%753,000</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>8.92%</t>
+          <t>8.96%</t>
         </is>
       </c>
       <c r="K2" t="n">
@@ -535,7 +535,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>-0.06%</t>
+          <t>+0.13%</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-01 03:32:06</t>
+          <t>2026-09-01 15:28:38</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -570,25 +570,25 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>-0.84%14180</t>
+          <t>-0.21%14150</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-0.84%</t>
+          <t>-0.21%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>14180</v>
+        <v>14150</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>5.60%80,000</t>
+          <t>5.61%80,000</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>5.60%</t>
+          <t>5.61%</t>
         </is>
       </c>
       <c r="K3" t="n">
@@ -596,7 +596,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>-0.05%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-01 03:32:06</t>
+          <t>2026-09-01 15:28:38</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -631,25 +631,25 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-1.51%3925</t>
+          <t>+9.94%4315</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-1.51%</t>
+          <t>+9.94%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>3925</v>
+        <v>4315</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>4.86%249,000</t>
+          <t>4.84%249,000</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>4.86%</t>
+          <t>4.84%</t>
         </is>
       </c>
       <c r="K4" t="n">
@@ -657,7 +657,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>-0.07%</t>
+          <t>+0.44%</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-01 03:32:06</t>
+          <t>2026-09-01 15:28:38</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -692,25 +692,25 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>+6.81%3530</t>
+          <t>-2.97%3425</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>+6.81%</t>
+          <t>-2.97%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>3530</v>
+        <v>3425</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>3.70%228,600</t>
+          <t>3.99%228,600</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>3.70%</t>
+          <t>3.99%</t>
         </is>
       </c>
       <c r="K5" t="n">
@@ -718,7 +718,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>+0.24%</t>
+          <t>-0.12%</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-01 03:32:06</t>
+          <t>2026-09-01 15:28:38</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -753,25 +753,25 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>-0.09%5485</t>
+          <t>+2.83%5640</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-0.09%</t>
+          <t>+2.83%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>5485</v>
+        <v>5640</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>3.66%136,000</t>
+          <t>3.69%136,000</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>3.66%</t>
+          <t>3.69%</t>
         </is>
       </c>
       <c r="K6" t="n">
@@ -779,7 +779,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.10%</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-01 03:32:06</t>
+          <t>2026-09-01 15:28:38</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -814,25 +814,25 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>+0.55%1840</t>
+          <t>+1.36%1865</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>+0.55%</t>
+          <t>+1.36%</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>1840</v>
+        <v>1865</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>3.62%404,000</t>
+          <t>3.68%404,000</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>3.62%</t>
+          <t>3.68%</t>
         </is>
       </c>
       <c r="K7" t="n">
@@ -840,7 +840,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>+0.05%</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-01 03:32:06</t>
+          <t>2026-09-01 15:28:38</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -870,38 +870,38 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>3037欣興電子</t>
+          <t>2408南亞科技</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>-10%999</t>
+          <t>-4.6%518</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-10%</t>
+          <t>-4.6%</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>999</v>
+        <v>518</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>3.06%563,000</t>
+          <t>2.95%1,096,000</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>3.06%</t>
+          <t>2.95%</t>
         </is>
       </c>
       <c r="K8" t="n">
-        <v>563000</v>
+        <v>1096000</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>-0.34%</t>
+          <t>-0.14%</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-01 03:32:06</t>
+          <t>2026-09-01 15:28:38</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -931,25 +931,25 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2408南亞科技</t>
+          <t>1303南亞塑膠工業</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>+0.56%543</t>
+          <t>-3.3%234.5</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>+0.56%</t>
+          <t>-3.3%</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>543</v>
+        <v>234.5</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2.90%1,096,000</t>
+          <t>2.90%2,416,000</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -958,11 +958,11 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>1096000</v>
+        <v>2416000</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>-0.10%</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-01 03:32:06</t>
+          <t>2026-09-01 15:28:38</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -992,38 +992,38 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>1303南亞塑膠工業</t>
+          <t>3037欣興電子</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>+9.98%242.5</t>
+          <t>-2.8%971</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>+9.98%</t>
+          <t>-2.8%</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>242.5</v>
+        <v>971</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2.61%2,416,000</t>
+          <t>2.78%563,000</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2.61%</t>
+          <t>2.78%</t>
         </is>
       </c>
       <c r="K10" t="n">
-        <v>2416000</v>
+        <v>563000</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>+0.24%</t>
+          <t>-0.08%</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-01 03:32:06</t>
+          <t>2026-09-01 15:28:38</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1058,16 +1058,16 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>-1.19%250</t>
+          <t>+2.4%256</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-1.19%</t>
+          <t>+2.4%</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>250</v>
+        <v>256</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>+0.06%</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-01 03:32:06</t>
+          <t>2026-09-01 15:28:38</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1114,38 +1114,38 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>7769鴻勁精密</t>
+          <t>2368金像電子（股）公司</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>-9.71%5860</t>
+          <t>+5.15%1225</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-9.71%</t>
+          <t>+5.15%</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>5860</v>
+        <v>1225</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>2.32%73,000</t>
+          <t>2.27%393,000</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2.32%</t>
+          <t>2.27%</t>
         </is>
       </c>
       <c r="K12" t="n">
-        <v>73000</v>
+        <v>393000</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>-0.25%</t>
+          <t>+0.11%</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-01 03:32:06</t>
+          <t>2026-09-01 15:28:38</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1180,25 +1180,25 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>+1.93%3425</t>
+          <t>-0.44%3410</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>+1.93%</t>
+          <t>-0.44%</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>3425</v>
+        <v>3410</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2.20%134,000</t>
+          <t>2.27%134,000</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2.20%</t>
+          <t>2.27%</t>
         </is>
       </c>
       <c r="K13" t="n">
@@ -1206,7 +1206,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>+0.04%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-01 03:32:06</t>
+          <t>2026-09-01 15:28:38</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1236,38 +1236,38 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2368金像電子（股）公司</t>
+          <t>7769鴻勁精密</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>+3.1%1165</t>
+          <t>+0.17%5870</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>+3.1%</t>
+          <t>+0.17%</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>1165</v>
+        <v>5870</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2.17%393,000</t>
+          <t>2.12%73,000</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2.17%</t>
+          <t>2.12%</t>
         </is>
       </c>
       <c r="K14" t="n">
-        <v>393000</v>
+        <v>73000</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>+0.07%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-01 03:32:06</t>
+          <t>2026-09-01 15:28:38</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1302,25 +1302,25 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>+0.7%2165</t>
+          <t>-1.85%2125</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>+0.7%</t>
+          <t>-1.85%</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>2165</v>
+        <v>2125</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2.07%197,000</t>
+          <t>2.11%197,000</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2.07%</t>
+          <t>2.11%</t>
         </is>
       </c>
       <c r="K15" t="n">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.04%</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-01 03:32:06</t>
+          <t>2026-09-01 15:28:38</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1363,25 +1363,25 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>+0.55%182.5</t>
+          <t>-3.56%176</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>+0.55%</t>
+          <t>-3.56%</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>182.5</v>
+        <v>176</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2.04%2,293,000</t>
+          <t>2.07%2,293,000</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2.04%</t>
+          <t>2.07%</t>
         </is>
       </c>
       <c r="K16" t="n">
@@ -1389,7 +1389,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.08%</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-01 03:32:08</t>
+          <t>2026-09-01 15:28:39</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1424,25 +1424,25 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>+3.54%5990</t>
+          <t>-1.75%5885</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>+3.54%</t>
+          <t>-1.75%</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>5990</v>
+        <v>5885</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>1.95%69,000</t>
+          <t>2.05%69,000</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>1.95%</t>
+          <t>2.05%</t>
         </is>
       </c>
       <c r="K17" t="n">
@@ -1450,7 +1450,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>+0.07%</t>
+          <t>-0.04%</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-01 03:32:08</t>
+          <t>2026-09-01 15:28:39</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1485,16 +1485,16 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>-1.46%7095</t>
+          <t>+9.94%7800</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-1.46%</t>
+          <t>+9.94%</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>7095</v>
+        <v>7800</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -1511,7 +1511,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>+0.17%</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-01 03:32:08</t>
+          <t>2026-09-01 15:28:39</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1541,38 +1541,38 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2345智邦科技</t>
+          <t>6223旺矽科技</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>-4.24%2035</t>
+          <t>+5.46%5410</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-4.24%</t>
+          <t>+5.46%</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>2035</v>
+        <v>5410</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1.81%174,000</t>
+          <t>1.83%72,000</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>1.81%</t>
+          <t>1.83%</t>
         </is>
       </c>
       <c r="K19" t="n">
-        <v>174000</v>
+        <v>72000</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>-0.08%</t>
+          <t>+0.10%</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-01 03:32:08</t>
+          <t>2026-09-01 15:28:39</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1602,38 +1602,38 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>6223旺矽科技</t>
+          <t>3443創意電子</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>+1.99%5130</t>
+          <t>-1.72%5995</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>+1.99%</t>
+          <t>-1.72%</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>5130</v>
+        <v>5995</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1.77%72,000</t>
+          <t>1.78%59,000</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>1.77%</t>
+          <t>1.78%</t>
         </is>
       </c>
       <c r="K20" t="n">
-        <v>72000</v>
+        <v>59000</v>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-01 03:32:08</t>
+          <t>2026-09-01 15:28:39</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1663,38 +1663,38 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2327國巨</t>
+          <t>2345智邦科技</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>-8.71%545</t>
+          <t>+8.35%2205</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-8.71%</t>
+          <t>+8.35%</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>545</v>
+        <v>2205</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>1.74%595,000</t>
+          <t>1.75%174,000</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>1.74%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="K21" t="n">
-        <v>595000</v>
+        <v>174000</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>-0.17%</t>
+          <t>+0.14%</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-01 03:32:08</t>
+          <t>2026-09-01 15:28:39</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1724,38 +1724,38 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>3443創意電子</t>
+          <t>6515穎崴科技</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>+1.41%6100</t>
+          <t>+9.94%6910</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>+1.41%</t>
+          <t>+9.94%</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>6100</v>
+        <v>6910</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>1.74%59,000</t>
+          <t>1.71%55,000</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>1.74%</t>
+          <t>1.71%</t>
         </is>
       </c>
       <c r="K22" t="n">
-        <v>59000</v>
+        <v>55000</v>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>+0.16%</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-01 03:32:08</t>
+          <t>2026-09-01 15:28:39</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1785,38 +1785,38 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>6515穎崴科技</t>
+          <t>2382廣達電腦</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>+0.56%6285</t>
+          <t>+1.03%342</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>+0.56%</t>
+          <t>+1.03%</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>6285</v>
+        <v>342</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>1.68%55,000</t>
+          <t>1.65%987,000</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>1.68%</t>
+          <t>1.65%</t>
         </is>
       </c>
       <c r="K23" t="n">
-        <v>55000</v>
+        <v>987000</v>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-01 03:32:08</t>
+          <t>2026-09-01 15:28:39</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1846,38 +1846,38 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2382廣達電腦</t>
+          <t>2327國巨</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>+1.8%338.5</t>
+          <t>+4.22%568</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>+1.8%</t>
+          <t>+4.22%</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>338.5</v>
+        <v>568</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>1.61%987,000</t>
+          <t>1.60%595,000</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>1.61%</t>
+          <t>1.60%</t>
         </is>
       </c>
       <c r="K24" t="n">
-        <v>987000</v>
+        <v>595000</v>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>+0.07%</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-01 03:32:08</t>
+          <t>2026-09-01 15:28:39</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1912,25 +1912,25 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>-5.96%584</t>
+          <t>+4.45%610</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>-5.96%</t>
+          <t>+4.45%</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>584</v>
+        <v>610</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>1.60%526,000</t>
+          <t>1.52%526,000</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>1.60%</t>
+          <t>1.52%</t>
         </is>
       </c>
       <c r="K25" t="n">
@@ -1938,7 +1938,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>-0.10%</t>
+          <t>+0.07%</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-01 03:32:08</t>
+          <t>2026-09-01 15:28:39</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1973,25 +1973,25 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>-3.69%1435</t>
+          <t>+1.05%1450</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-3.69%</t>
+          <t>+1.05%</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>1435</v>
+        <v>1450</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>1.52%209,000</t>
+          <t>1.48%209,000</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>1.52%</t>
+          <t>1.48%</t>
         </is>
       </c>
       <c r="K26" t="n">
@@ -1999,7 +1999,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>-0.06%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-01 03:32:08</t>
+          <t>2026-09-01 15:28:39</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2029,38 +2029,38 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2360致茂電子</t>
+          <t>5274信驊科技</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>-2.49%1960</t>
+          <t>+6.57%17120</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-2.49%</t>
+          <t>+6.57%</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>1960</v>
+        <v>17120</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>1.46%148,000</t>
+          <t>1.45%18,300</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>1.46%</t>
+          <t>1.45%</t>
         </is>
       </c>
       <c r="K27" t="n">
-        <v>148000</v>
+        <v>18300</v>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>+0.09%</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-01 03:32:08</t>
+          <t>2026-09-01 15:28:39</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2095,25 +2095,25 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>+0.47%64.7</t>
+          <t>+2.78%66.5</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>+0.47%</t>
+          <t>+2.78%</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>64.7</v>
+        <v>66.5</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>1.43%4,525,000</t>
+          <t>1.45%4,525,000</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>1.43%</t>
+          <t>1.45%</t>
         </is>
       </c>
       <c r="K28" t="n">
@@ -2121,7 +2121,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>+0.04%</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-01 03:32:08</t>
+          <t>2026-09-01 15:28:39</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2151,38 +2151,38 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>5274信驊科技</t>
+          <t>2360致茂電子</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>+2.78%16065</t>
+          <t>+3.57%2030</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>+2.78%</t>
+          <t>+3.57%</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>16065</v>
+        <v>2030</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>1.40%18,300</t>
+          <t>1.44%148,000</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>1.40%</t>
+          <t>1.44%</t>
         </is>
       </c>
       <c r="K29" t="n">
-        <v>18300</v>
+        <v>148000</v>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>+0.04%</t>
+          <t>+0.05%</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-01 03:32:08</t>
+          <t>2026-09-01 15:28:39</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2217,25 +2217,25 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>-5.84%548</t>
+          <t>+0.36%550</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>-5.84%</t>
+          <t>+0.36%</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>1.37%482,000</t>
+          <t>1.31%482,000</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>1.37%</t>
+          <t>1.31%</t>
         </is>
       </c>
       <c r="K30" t="n">
@@ -2243,7 +2243,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>-0.08%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-01 03:32:08</t>
+          <t>2026-09-01 15:28:39</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2273,38 +2273,38 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>8046南亞電路板</t>
+          <t>2884玉山金融控股</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>-0.81%1230</t>
+          <t>+0.38%39.9</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>-0.81%</t>
+          <t>+0.38%</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>1230</v>
+        <v>39.9</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>1.23%203,000</t>
+          <t>1.25%6,340,622</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>1.23%</t>
+          <t>1.25%</t>
         </is>
       </c>
       <c r="K31" t="n">
-        <v>203000</v>
+        <v>6340622</v>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-01 03:32:09</t>
+          <t>2026-09-01 15:28:40</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2334,38 +2334,38 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2884玉山金融控股</t>
+          <t>8046南亞電路板</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>+2.58%39.75</t>
+          <t>-0.41%1225</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>+2.58%</t>
+          <t>-0.41%</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>39.75</v>
+        <v>1225</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>1.20%6,340,622</t>
+          <t>1.24%203,000</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>1.20%</t>
+          <t>1.24%</t>
         </is>
       </c>
       <c r="K32" t="n">
-        <v>6340622</v>
+        <v>203000</v>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-01 03:32:09</t>
+          <t>2026-09-01 15:28:40</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2400,25 +2400,25 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>+2.58%358</t>
+          <t>+0.28%359</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>+2.58%</t>
+          <t>+0.28%</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>1.19%694,000</t>
+          <t>1.23%694,000</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>1.19%</t>
+          <t>1.23%</t>
         </is>
       </c>
       <c r="K33" t="n">
@@ -2426,7 +2426,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-01 03:32:09</t>
+          <t>2026-09-01 15:28:40</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2461,25 +2461,25 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>+1.08%75</t>
+          <t>-2%73.5</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>+1.08%</t>
+          <t>-2%</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>75</v>
+        <v>73.5</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>1.14%3,124,500</t>
+          <t>1.16%3,124,500</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>1.14%</t>
+          <t>1.16%</t>
         </is>
       </c>
       <c r="K34" t="n">
@@ -2487,7 +2487,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-01 03:32:09</t>
+          <t>2026-09-01 15:28:40</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2517,38 +2517,38 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>8996高力熱處理工業</t>
+          <t>4958臻鼎科技控股</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>-7.11%1175</t>
+          <t>+7%535</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>-7.11%</t>
+          <t>+7%</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>1175</v>
+        <v>535</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>1.12%181,000</t>
+          <t>1.14%461,000</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>1.12%</t>
+          <t>1.14%</t>
         </is>
       </c>
       <c r="K35" t="n">
-        <v>181000</v>
+        <v>461000</v>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>-0.09%</t>
+          <t>+0.08%</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-01 03:32:09</t>
+          <t>2026-09-01 15:28:40</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>1.10%1,147,000</t>
+          <t>1.11%1,147,000</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>1.10%</t>
+          <t>1.11%</t>
         </is>
       </c>
       <c r="K36" t="n">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-01 03:32:09</t>
+          <t>2026-09-01 15:28:40</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2639,38 +2639,38 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>4958臻鼎科技控股</t>
+          <t>8996高力熱處理工業</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>+4.06%500</t>
+          <t>0%1175</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>+4.06%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>500</v>
+        <v>1175</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>1.08%461,000</t>
+          <t>1.05%181,000</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>1.08%</t>
+          <t>1.05%</t>
         </is>
       </c>
       <c r="K37" t="n">
-        <v>461000</v>
+        <v>181000</v>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>+0.04%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-01 03:32:09</t>
+          <t>2026-09-01 15:28:40</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2700,38 +2700,38 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>8210勤誠興業</t>
+          <t>3008大立光電</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>-2.12%969</t>
+          <t>-0.92%7580</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>-2.12%</t>
+          <t>-0.92%</t>
         </is>
       </c>
       <c r="H38" t="n">
-        <v>969</v>
+        <v>7580</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>0.94%193,000</t>
+          <t>0.98%26,000</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>0.94%</t>
+          <t>0.98%</t>
         </is>
       </c>
       <c r="K38" t="n">
-        <v>193000</v>
+        <v>26000</v>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-01 03:32:09</t>
+          <t>2026-09-01 15:28:40</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2761,38 +2761,38 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>3231緯創資通</t>
+          <t>8210勤誠興業</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>0%178</t>
+          <t>+2.17%990</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>+2.17%</t>
         </is>
       </c>
       <c r="H39" t="n">
-        <v>178</v>
+        <v>990</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>0.91%1,041,000</t>
+          <t>0.93%193,000</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>0.91%</t>
+          <t>0.93%</t>
         </is>
       </c>
       <c r="K39" t="n">
-        <v>1041000</v>
+        <v>193000</v>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-01 03:32:09</t>
+          <t>2026-09-01 15:28:40</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2822,38 +2822,38 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>3008大立光電</t>
+          <t>3231緯創資通</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>+8.28%7650</t>
+          <t>+2.25%182</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>+8.28%</t>
+          <t>+2.25%</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>7650</v>
+        <v>182</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>0.90%26,000</t>
+          <t>0.92%1,041,000</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>0.90%</t>
+          <t>0.92%</t>
         </is>
       </c>
       <c r="K40" t="n">
-        <v>26000</v>
+        <v>1041000</v>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>+0.07%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-01 03:32:09</t>
+          <t>2026-09-01 15:28:40</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2888,25 +2888,25 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>+3.25%730</t>
+          <t>-2.6%711</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>+3.25%</t>
+          <t>-2.6%</t>
         </is>
       </c>
       <c r="H41" t="n">
-        <v>730</v>
+        <v>711</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>0.87%252,000</t>
+          <t>0.91%252,000</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>0.87%</t>
+          <t>0.91%</t>
         </is>
       </c>
       <c r="K41" t="n">
@@ -2914,7 +2914,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-01 03:32:09</t>
+          <t>2026-09-01 15:28:40</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2949,25 +2949,25 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>+1.33%496.5</t>
+          <t>+1.31%503</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>+1.33%</t>
+          <t>+1.31%</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>496.5</v>
+        <v>503</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>0.83%345,000</t>
+          <t>0.85%345,000</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>0.83%</t>
+          <t>0.85%</t>
         </is>
       </c>
       <c r="K42" t="n">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-01 03:32:09</t>
+          <t>2026-09-01 15:28:40</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3010,25 +3010,25 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>-8.9%819</t>
+          <t>+6.72%874</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>-8.9%</t>
+          <t>+6.72%</t>
         </is>
       </c>
       <c r="H43" t="n">
-        <v>819</v>
+        <v>874</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>0.81%185,000</t>
+          <t>0.75%185,000</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>0.81%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="K43" t="n">
@@ -3036,7 +3036,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>-0.08%</t>
+          <t>+0.05%</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-01 03:32:09</t>
+          <t>2026-09-01 15:28:40</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3071,25 +3071,25 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>-2.98%228</t>
+          <t>+4.17%237.5</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>-2.98%</t>
+          <t>+4.17%</t>
         </is>
       </c>
       <c r="H44" t="n">
-        <v>228</v>
+        <v>237.5</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>0.75%650,000</t>
+          <t>0.73%650,000</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>0.75%</t>
+          <t>0.73%</t>
         </is>
       </c>
       <c r="K44" t="n">
@@ -3097,7 +3097,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-01 03:32:09</t>
+          <t>2026-09-01 15:28:40</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3132,16 +3132,16 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>-1.71%2305</t>
+          <t>-0.87%2285</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>-1.71%</t>
+          <t>-0.87%</t>
         </is>
       </c>
       <c r="H45" t="n">
-        <v>2305</v>
+        <v>2285</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-01 03:32:09</t>
+          <t>2026-09-01 15:28:40</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3193,25 +3193,25 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>-0.32%618</t>
+          <t>-1.46%609</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>-0.32%</t>
+          <t>-1.46%</t>
         </is>
       </c>
       <c r="H46" t="n">
-        <v>618</v>
+        <v>609</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>0.55%182,000</t>
+          <t>0.56%182,000</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>0.55%</t>
+          <t>0.56%</t>
         </is>
       </c>
       <c r="K46" t="n">
@@ -3219,7 +3219,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-09-01 03:32:10</t>
+          <t>2026-09-01 15:28:41</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3254,25 +3254,25 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>-5.51%2400</t>
+          <t>+10%2640</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>-5.51%</t>
+          <t>+10%</t>
         </is>
       </c>
       <c r="H47" t="n">
-        <v>2400</v>
+        <v>2640</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>0.55%44,000</t>
+          <t>0.52%44,000</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>0.55%</t>
+          <t>0.52%</t>
         </is>
       </c>
       <c r="K47" t="n">
@@ -3280,7 +3280,7 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>+0.05%</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-09-01 03:32:10</t>
+          <t>2026-09-01 15:28:41</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3315,16 +3315,16 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>0%742</t>
+          <t>-1.48%731</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-1.48%</t>
         </is>
       </c>
       <c r="H48" t="n">
-        <v>742</v>
+        <v>731</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
@@ -3341,7 +3341,7 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-01 03:32:10</t>
+          <t>2026-09-01 15:28:41</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3376,25 +3376,25 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>-3.98%2170</t>
+          <t>+6.68%2315</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>-3.98%</t>
+          <t>+6.68%</t>
         </is>
       </c>
       <c r="H49" t="n">
-        <v>2170</v>
+        <v>2315</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>0.36%32,336</t>
+          <t>0.35%32,336</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>0.36%</t>
+          <t>0.35%</t>
         </is>
       </c>
       <c r="K49" t="n">
@@ -3402,7 +3402,7 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-09-01 03:32:10</t>
+          <t>2026-09-01 15:28:41</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3432,38 +3432,38 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>3533嘉澤端子工業</t>
+          <t>6442光紅建聖</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>-2.59%1690</t>
+          <t>+0.31%1635</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>-2.59%</t>
+          <t>+0.31%</t>
         </is>
       </c>
       <c r="H50" t="n">
-        <v>1690</v>
+        <v>1635</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>0.30%35,000</t>
+          <t>0.31%38,000</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.31%</t>
         </is>
       </c>
       <c r="K50" t="n">
-        <v>35000</v>
+        <v>38000</v>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-09-01 03:32:10</t>
+          <t>2026-09-01 15:28:41</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3493,38 +3493,38 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>6442光紅建聖</t>
+          <t>3533嘉澤端子工業</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>+0.93%1630</t>
+          <t>+3.25%1745</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>+0.93%</t>
+          <t>+3.25%</t>
         </is>
       </c>
       <c r="H51" t="n">
-        <v>1630</v>
+        <v>1745</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>0.30%38,000</t>
+          <t>0.29%35,000</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.29%</t>
         </is>
       </c>
       <c r="K51" t="n">
-        <v>38000</v>
+        <v>35000</v>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">

--- a/etf_holdings/2026-09-01_00980A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-01_00980A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-01 15:28:38</t>
+          <t>2026-09-01 15:55:29</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-01 15:28:38</t>
+          <t>2026-09-01 15:55:29</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-01 15:28:38</t>
+          <t>2026-09-01 15:55:29</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-01 15:28:38</t>
+          <t>2026-09-01 15:55:29</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-01 15:28:38</t>
+          <t>2026-09-01 15:55:29</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-01 15:28:38</t>
+          <t>2026-09-01 15:55:29</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-01 15:28:38</t>
+          <t>2026-09-01 15:55:29</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-01 15:28:38</t>
+          <t>2026-09-01 15:55:29</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-01 15:28:38</t>
+          <t>2026-09-01 15:55:29</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-01 15:28:38</t>
+          <t>2026-09-01 15:55:29</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-01 15:28:38</t>
+          <t>2026-09-01 15:55:29</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-01 15:28:38</t>
+          <t>2026-09-01 15:55:29</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-01 15:28:38</t>
+          <t>2026-09-01 15:55:29</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-01 15:28:38</t>
+          <t>2026-09-01 15:55:29</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-01 15:28:38</t>
+          <t>2026-09-01 15:55:29</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-01 15:28:39</t>
+          <t>2026-09-01 15:55:30</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-01 15:28:39</t>
+          <t>2026-09-01 15:55:30</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-01 15:28:39</t>
+          <t>2026-09-01 15:55:30</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-01 15:28:39</t>
+          <t>2026-09-01 15:55:30</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-01 15:28:39</t>
+          <t>2026-09-01 15:55:30</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-01 15:28:39</t>
+          <t>2026-09-01 15:55:30</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-01 15:28:39</t>
+          <t>2026-09-01 15:55:30</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-01 15:28:39</t>
+          <t>2026-09-01 15:55:30</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-01 15:28:39</t>
+          <t>2026-09-01 15:55:30</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-01 15:28:39</t>
+          <t>2026-09-01 15:55:30</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-01 15:28:39</t>
+          <t>2026-09-01 15:55:30</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-01 15:28:39</t>
+          <t>2026-09-01 15:55:30</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-01 15:28:39</t>
+          <t>2026-09-01 15:55:30</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-01 15:28:39</t>
+          <t>2026-09-01 15:55:30</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-01 15:28:39</t>
+          <t>2026-09-01 15:55:30</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-01 15:28:40</t>
+          <t>2026-09-01 15:55:31</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-01 15:28:40</t>
+          <t>2026-09-01 15:55:31</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-01 15:28:40</t>
+          <t>2026-09-01 15:55:31</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-01 15:28:40</t>
+          <t>2026-09-01 15:55:31</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-01 15:28:40</t>
+          <t>2026-09-01 15:55:31</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-01 15:28:40</t>
+          <t>2026-09-01 15:55:31</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-01 15:28:40</t>
+          <t>2026-09-01 15:55:31</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-01 15:28:40</t>
+          <t>2026-09-01 15:55:31</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-01 15:28:40</t>
+          <t>2026-09-01 15:55:31</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-01 15:28:40</t>
+          <t>2026-09-01 15:55:31</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-01 15:28:40</t>
+          <t>2026-09-01 15:55:31</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-01 15:28:40</t>
+          <t>2026-09-01 15:55:31</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-01 15:28:40</t>
+          <t>2026-09-01 15:55:31</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-01 15:28:40</t>
+          <t>2026-09-01 15:55:31</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-01 15:28:40</t>
+          <t>2026-09-01 15:55:31</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-09-01 15:28:41</t>
+          <t>2026-09-01 15:55:33</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-09-01 15:28:41</t>
+          <t>2026-09-01 15:55:33</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-01 15:28:41</t>
+          <t>2026-09-01 15:55:33</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-09-01 15:28:41</t>
+          <t>2026-09-01 15:55:33</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-09-01 15:28:41</t>
+          <t>2026-09-01 15:55:33</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">

--- a/etf_holdings/2026-09-01_00980A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-01_00980A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-01 15:55:29</t>
+          <t>2026-09-01 19:35:30</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-01 15:55:29</t>
+          <t>2026-09-01 19:35:30</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-01 15:55:29</t>
+          <t>2026-09-01 19:35:30</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-01 15:55:29</t>
+          <t>2026-09-01 19:35:30</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-01 15:55:29</t>
+          <t>2026-09-01 19:35:30</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-01 15:55:29</t>
+          <t>2026-09-01 19:35:30</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-01 15:55:29</t>
+          <t>2026-09-01 19:35:30</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-01 15:55:29</t>
+          <t>2026-09-01 19:35:30</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-01 15:55:29</t>
+          <t>2026-09-01 19:35:30</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-01 15:55:29</t>
+          <t>2026-09-01 19:35:30</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-01 15:55:29</t>
+          <t>2026-09-01 19:35:30</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-01 15:55:29</t>
+          <t>2026-09-01 19:35:30</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-01 15:55:29</t>
+          <t>2026-09-01 19:35:30</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-01 15:55:29</t>
+          <t>2026-09-01 19:35:30</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-01 15:55:29</t>
+          <t>2026-09-01 19:35:30</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-01 15:55:30</t>
+          <t>2026-09-01 19:35:32</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-01 15:55:30</t>
+          <t>2026-09-01 19:35:32</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-01 15:55:30</t>
+          <t>2026-09-01 19:35:32</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-01 15:55:30</t>
+          <t>2026-09-01 19:35:32</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-01 15:55:30</t>
+          <t>2026-09-01 19:35:32</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-01 15:55:30</t>
+          <t>2026-09-01 19:35:32</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-01 15:55:30</t>
+          <t>2026-09-01 19:35:32</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-01 15:55:30</t>
+          <t>2026-09-01 19:35:32</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-01 15:55:30</t>
+          <t>2026-09-01 19:35:32</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-01 15:55:30</t>
+          <t>2026-09-01 19:35:32</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-01 15:55:30</t>
+          <t>2026-09-01 19:35:32</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-01 15:55:30</t>
+          <t>2026-09-01 19:35:32</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-01 15:55:30</t>
+          <t>2026-09-01 19:35:32</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-01 15:55:30</t>
+          <t>2026-09-01 19:35:32</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-01 15:55:30</t>
+          <t>2026-09-01 19:35:32</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-01 15:55:31</t>
+          <t>2026-09-01 19:35:33</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-01 15:55:31</t>
+          <t>2026-09-01 19:35:33</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-01 15:55:31</t>
+          <t>2026-09-01 19:35:33</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-01 15:55:31</t>
+          <t>2026-09-01 19:35:33</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-01 15:55:31</t>
+          <t>2026-09-01 19:35:33</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-01 15:55:31</t>
+          <t>2026-09-01 19:35:33</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-01 15:55:31</t>
+          <t>2026-09-01 19:35:33</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-01 15:55:31</t>
+          <t>2026-09-01 19:35:33</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-01 15:55:31</t>
+          <t>2026-09-01 19:35:33</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-01 15:55:31</t>
+          <t>2026-09-01 19:35:33</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-01 15:55:31</t>
+          <t>2026-09-01 19:35:33</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-01 15:55:31</t>
+          <t>2026-09-01 19:35:33</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-01 15:55:31</t>
+          <t>2026-09-01 19:35:33</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-01 15:55:31</t>
+          <t>2026-09-01 19:35:33</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-01 15:55:31</t>
+          <t>2026-09-01 19:35:33</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-09-01 15:55:33</t>
+          <t>2026-09-01 19:35:34</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-09-01 15:55:33</t>
+          <t>2026-09-01 19:35:34</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-01 15:55:33</t>
+          <t>2026-09-01 19:35:34</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-09-01 15:55:33</t>
+          <t>2026-09-01 19:35:34</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-09-01 15:55:33</t>
+          <t>2026-09-01 19:35:34</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
